--- a/港岛-湾仔-Woodis/Woodis_销控明细表.xlsx
+++ b/港岛-湾仔-Woodis/Woodis_销控明细表.xlsx
@@ -2451,7 +2451,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8593,7 +8593,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8655,7 +8655,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11914,7 +11914,7 @@
           <t>C | 377呎 (2房)
 $971万
 $25,753/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -11977,7 +11977,7 @@
           <t>C | 377呎 (2房)
 $961万
 $25,499/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -11985,7 +11985,7 @@
           <t>D | 343呎 (2房)
 $847万
 $24,687/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -11993,7 +11993,7 @@
           <t>E | 346呎 (2房)
 $862万
 $24,906/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -12001,7 +12001,7 @@
           <t>F | 431呎 (2房)
 $1217万
 $28,236/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -12024,7 +12024,7 @@
           <t>A | 598呎 (3房)
 $1875万
 $31,358/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -12040,7 +12040,7 @@
           <t>C | 377呎 (2房)
 $922万
 $24,447/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -12048,7 +12048,7 @@
           <t>D | 343呎 (2房)
 $831万
 $24,217/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -12056,7 +12056,7 @@
           <t>E | 346呎 (2房)
 $900万
 $26,002/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -12064,7 +12064,7 @@
           <t>F | 431呎 (2房)
 $1177万
 $27,316/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -12072,7 +12072,7 @@
           <t>G | 426呎 (2房)
 $1270万
 $29,819/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
     </row>
@@ -12087,7 +12087,7 @@
           <t>A | 598呎 (3房)
 $1820万
 $30,441/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -12103,7 +12103,7 @@
           <t>C | 377呎 (2房)
 $945万
 $25,073/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -12111,7 +12111,7 @@
           <t>D | 343呎 (2房)
 $809万
 $23,600/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -12119,7 +12119,7 @@
           <t>E | 346呎 (2房)
 $840万
 $24,282/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -12127,7 +12127,7 @@
           <t>F | 431呎 (2房)
 $1137万
 $26,373/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -12135,7 +12135,7 @@
           <t>G | 426呎 (2房)
 $1169万
 $27,438/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12166,7 @@
           <t>C | 377呎 (2房)
 $939万
 $24,904/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -12174,7 +12174,7 @@
           <t>D | 343呎 (2房)
 $770万
 $22,464/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -12182,7 +12182,7 @@
           <t>E | 346呎 (2房)
 $782万
 $22,598/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -12190,7 +12190,7 @@
           <t>F | 431呎 (2房)
 $1119万
 $25,965/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -12198,7 +12198,7 @@
           <t>G | 426呎 (2房)
 $1194万
 $28,039/呎
-(25年-10月-24日)</t>
+(25年-10月-25日)</t>
         </is>
       </c>
     </row>
@@ -12213,7 +12213,7 @@
           <t>A | 598呎 (3房)
 $1711万
 $28,607/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -12229,7 +12229,7 @@
           <t>C | 377呎 (2房)
 $933万
 $24,735/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -12237,7 +12237,7 @@
           <t>D | 343呎 (2房)
 $799万
 $23,283/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -12245,7 +12245,7 @@
           <t>E | 346呎 (2房)
 $774万
 $22,375/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -12253,7 +12253,7 @@
           <t>F | 431呎 (2房)
 $1108万
 $25,705/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -12261,7 +12261,7 @@
           <t>G | 426呎 (2房)
 $1121万
 $26,326/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12276,7 @@
           <t>A | 598呎 (3房)
 $1545万
 $25,843/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -12292,7 +12292,7 @@
           <t>C | 377呎 (2房)
 $897万
 $23,788/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -12300,7 +12300,7 @@
           <t>D | 343呎 (2房)
 $758万
 $22,085/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -12308,7 +12308,7 @@
           <t>E | 346呎 (2房)
 $766万
 $22,149/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -12316,7 +12316,7 @@
           <t>F | 431呎 (2房)
 $1097万
 $25,447/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -12324,7 +12324,7 @@
           <t>G | 426呎 (2房)
 $1107万
 $25,976/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
           <t>A | 598呎 (3房)
 $1524万
 $25,480/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -12355,7 +12355,7 @@
           <t>C | 377呎 (2房)
 $967万
 $25,655/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -12363,7 +12363,7 @@
           <t>D | 343呎 (2房)
 $750万
 $21,857/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -12371,7 +12371,7 @@
           <t>E | 346呎 (2房)
 $759万
 $21,923/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -12379,7 +12379,7 @@
           <t>F | 431呎 (2房)
 $1086万
 $25,189/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -12387,7 +12387,7 @@
           <t>G | 426呎 (2房)
 $1061万
 $24,903/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
           <t>A | 598呎 (3房)
 $1552万
 $25,952/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -12418,7 +12418,7 @@
           <t>C | 377呎 (2房)
 $884万
 $23,461/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -12426,7 +12426,7 @@
           <t>D | 343呎 (2房)
 $742万
 $21,632/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -12434,7 +12434,7 @@
           <t>E | 346呎 (2房)
 $751万
 $21,697/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -12442,7 +12442,7 @@
           <t>F | 431呎 (2房)
 $1041万
 $24,142/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -12450,7 +12450,7 @@
           <t>G | 426呎 (2房)
 $1081万
 $25,365/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -12465,7 +12465,7 @@
           <t>A | 598呎 (3房)
 $1482万
 $24,785/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -12481,7 +12481,7 @@
           <t>C | 377呎 (2房)
 $905万
 $23,993/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -12497,7 +12497,7 @@
           <t>E | 346呎 (2房)
 $746万
 $21,548/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -12505,7 +12505,7 @@
           <t>F | 431呎 (2房)
 $1030万
 $23,892/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -12513,7 +12513,7 @@
           <t>G | 426呎 (2房)
 $1077万
 $25,280/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -12528,7 +12528,7 @@
           <t>A | 598呎 (3房)
 $1472万
 $24,611/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -12544,7 +12544,7 @@
           <t>C | 377呎 (2房)
 $872万
 $23,132/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -12552,7 +12552,7 @@
           <t>D | 343呎 (2房)
 $755万
 $22,024/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -12560,7 +12560,7 @@
           <t>E | 346呎 (2房)
 $740万
 $21,397/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -12568,7 +12568,7 @@
           <t>F | 431呎 (2房)
 $1023万
 $23,726/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -12576,7 +12576,7 @@
           <t>G | 426呎 (2房)
 $1025万
 $24,058/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -12591,7 +12591,7 @@
           <t>A | 598呎 (3房)
 $1509万
 $25,234/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -12607,7 +12607,7 @@
           <t>C | 377呎 (2房)
 $866万
 $22,966/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -12631,7 +12631,7 @@
           <t>F | 431呎 (2房)
 $1015万
 $23,557/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -12639,7 +12639,7 @@
           <t>G | 426呎 (2房)
 $1045万
 $24,533/呎
-(25年-10月-24日)</t>
+(25年-10月-25日)</t>
         </is>
       </c>
     </row>
@@ -12654,7 +12654,7 @@
           <t>A | 598呎 (3房)
 $1509万
 $25,228/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -12662,7 +12662,7 @@
           <t>B | 282呎 (1房)
 $720万
 $25,533/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -12670,7 +12670,7 @@
           <t>C | 377呎 (2房)
 $885万
 $23,485/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -12678,7 +12678,7 @@
           <t>D | 343呎 (2房)
 $721万
 $21,026/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -12686,7 +12686,7 @@
           <t>E | 346呎 (2房)
 $730万
 $21,096/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -12694,7 +12694,7 @@
           <t>F | 431呎 (2房)
 $1008万
 $23,390/呎
-(25年-10月-17日)</t>
+(25年-10月-18日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -12702,7 +12702,7 @@
           <t>G | 426呎 (2房)
 $1010万
 $23,719/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -12717,7 +12717,7 @@
           <t>A | 598呎 (3房)
 $1425万
 $23,829/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -12725,7 +12725,7 @@
           <t>B | 282呎 (1房)
 $715万
 $25,347/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -12733,7 +12733,7 @@
           <t>C | 377呎 (2房)
 $853万
 $22,639/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -12757,7 +12757,7 @@
           <t>F | 431呎 (2房)
 $1030万
 $23,895/呎
-(25年-10月-17日)</t>
+(25年-10月-18日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -12765,7 +12765,7 @@
           <t>G | 426呎 (2房)
 $1030万
 $24,185/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -12780,7 +12780,7 @@
           <t>A | 598呎 (3房)
 $1399万
 $23,394/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -12788,7 +12788,7 @@
           <t>B | 282呎 (1房)
 $676万
 $23,966/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -12796,7 +12796,7 @@
           <t>C | 377呎 (2房)
 $874万
 $23,193/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -12804,7 +12804,7 @@
           <t>D | 343呎 (2房)
 $734万
 $21,396/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -12812,7 +12812,7 @@
           <t>E | 346呎 (2房)
 $738万
 $21,320/呎
-(25年-10月-17日)</t>
+(25年-10月-18日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -12820,7 +12820,7 @@
           <t>F | 431呎 (2房)
 $983万
 $22,806/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -12828,7 +12828,7 @@
           <t>G | 426呎 (2房)
 $996万
 $23,382/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
     </row>
@@ -12843,7 +12843,7 @@
           <t>A | 598呎 (3房)
 $1373万
 $22,965/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -12851,7 +12851,7 @@
           <t>B | 282呎 (1房)
 $710万
 $25,185/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -12859,7 +12859,7 @@
           <t>C | 377呎 (2房)
 $844万
 $22,395/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -12867,7 +12867,7 @@
           <t>D | 343呎 (2房)
 $706万
 $20,570/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -12875,7 +12875,7 @@
           <t>E | 346呎 (2房)
 $705万
 $20,389/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -12883,7 +12883,7 @@
           <t>F | 431呎 (2房)
 $1000万
 $23,206/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -12891,7 +12891,7 @@
           <t>G | 426呎 (2房)
 $989万
 $23,212/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12906,7 @@
           <t>A | 598呎 (3房)
 $1347万
 $22,525/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -12914,7 +12914,7 @@
           <t>B | 282呎 (1房)
 $671万
 $23,806/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -12946,7 +12946,7 @@
           <t>F | 431呎 (2房)
 $951万
 $22,054/呎
-(25年-10月-17日)</t>
+(25年-10月-18日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -12954,7 +12954,7 @@
           <t>G | 426呎 (2房)
 $1014万
 $23,795/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12969,7 @@
           <t>A | 598呎 (3房)
 $1321万
 $22,089/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -12977,7 +12977,7 @@
           <t>B | 282呎 (1房)
 $669万
 $23,740/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -12985,7 +12985,7 @@
           <t>C | 377呎 (2房)
 $865万
 $22,954/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -13009,7 +13009,7 @@
           <t>F | 431呎 (2房)
 $943万
 $21,888/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -13017,7 +13017,7 @@
           <t>G | 426呎 (2房)
 $1006万
 $23,621/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
     </row>
@@ -13032,7 +13032,7 @@
           <t>A | 598呎 (3房)
 $1337万
 $22,360/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -13040,7 +13040,7 @@
           <t>B | 282呎 (1房)
 $664万
 $23,561/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -13072,7 +13072,7 @@
           <t>F | 431呎 (2房)
 $936万
 $21,719/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -13080,7 +13080,7 @@
           <t>G | 426呎 (2房)
 $999万
 $23,447/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -13095,7 +13095,7 @@
           <t>A | 598呎 (3房)
 $1310万
 $21,912/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -13103,7 +13103,7 @@
           <t>B | 282呎 (1房)
 $659万
 $23,359/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -13143,7 +13143,7 @@
           <t>G | 426呎 (2房)
 $994万
 $23,324/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
     </row>
@@ -13166,7 +13166,7 @@
           <t>B | 244呎 (1房)
 $662万
 $27,143/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -13174,7 +13174,7 @@
           <t>C | 339呎 (2房)
 $930万
 $27,423/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
